--- a/data/broadcast_graphics.xlsx
+++ b/data/broadcast_graphics.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:A2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -416,47 +416,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Имя спортсмена</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Фото URL</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Город</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Разряд</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Этап</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Попытка</v>
+        <v>Статус</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Анар Алиев</v>
-      </c>
-      <c r="B2" t="str">
-        <v>https://s3.outscore.ru/user/9/1000028178.jpg</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Калининград</v>
-      </c>
-      <c r="D2" t="str">
-        <v>МС</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Финал</v>
-      </c>
-      <c r="F2" t="str">
-        <v>ВТОРАЯ ПОПЫТКА</v>
+        <v>Нет активного заезда</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1892,124 +1862,28 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:A2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>competition_name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>event_name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>rider_name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>rider_first_name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>rider_last_name</v>
-      </c>
-      <c r="F1" t="str">
-        <v>rider_photo</v>
-      </c>
-      <c r="G1" t="str">
-        <v>rider_city</v>
-      </c>
-      <c r="H1" t="str">
-        <v>rider_rank</v>
-      </c>
-      <c r="I1" t="str">
-        <v>stage_name</v>
-      </c>
-      <c r="J1" t="str">
-        <v>attempt</v>
-      </c>
-      <c r="K1" t="str">
-        <v>attempt_text</v>
-      </c>
-      <c r="L1" t="str">
-        <v>current_score</v>
-      </c>
-      <c r="M1" t="str">
-        <v>status</v>
-      </c>
-      <c r="N1" t="str">
-        <v>tricks_count</v>
-      </c>
-      <c r="O1" t="str">
-        <v>total_degrees</v>
-      </c>
-      <c r="P1" t="str">
-        <v>total_tailwhips</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>total_barspins</v>
+        <v>Статус</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Альфа-Банк Кубок России по BMX Фристайл 2026</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1ый этап. Красноярск. Мужчины 19 лет и старше</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Анар Алиев</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Анар</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Алиев</v>
-      </c>
-      <c r="F2" t="str">
-        <v>https://s3.outscore.ru/user/9/1000028178.jpg</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Калининград</v>
-      </c>
-      <c r="H2" t="str">
-        <v>МС</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Финал</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2" t="str">
-        <v>ВТОРАЯ ПОПЫТКА</v>
-      </c>
-      <c r="L2" t="str">
-        <v>34.67</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Завершено</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="O2">
-        <v>2340</v>
-      </c>
-      <c r="P2">
-        <v>6</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
+        <v>Нет активного заезда</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:A2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -2018,73 +1892,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Время (сек)</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Код трюка</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Название трюка</v>
+        <v>Статус</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>23.87</v>
-      </c>
-      <c r="B2" t="str">
-        <v>o-3w</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Opposite + 3x tailwhip</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>16.67</v>
-      </c>
-      <c r="B3" t="str">
-        <v>q-t-2w</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Quarter/Air + Transfer + 2x tailwhip</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>11.84</v>
-      </c>
-      <c r="B4" t="str">
-        <v>flip-b</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Backflip + Barspin</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>6.95</v>
-      </c>
-      <c r="B5" t="str">
-        <v>3-w</v>
-      </c>
-      <c r="C5" t="str">
-        <v>360° + Tailwhip</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>4.45</v>
-      </c>
-      <c r="B6" t="str">
-        <v>10</v>
-      </c>
-      <c r="C6" t="str">
-        <v>1080°</v>
+        <v>Нет данных о трюках</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2257,7 +2075,7 @@
         <v>Последнее обновление</v>
       </c>
       <c r="B8" t="str">
-        <v>03.04.2026, 14:48:11</v>
+        <v>03.04.2026, 15:02:22</v>
       </c>
     </row>
   </sheetData>
